--- a/artfynd/A 30664-2026 artfynd.xlsx
+++ b/artfynd/A 30664-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136420642</v>
       </c>
       <c r="B2" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136420658</v>
       </c>
       <c r="B3" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136420666</v>
       </c>
       <c r="B4" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136420782</v>
       </c>
       <c r="B5" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136420948</v>
       </c>
       <c r="B6" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>136420975</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136420608</v>
       </c>
       <c r="B8" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>136420857</v>
       </c>
       <c r="B9" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136420966</v>
       </c>
       <c r="B10" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136420979</v>
       </c>
       <c r="B11" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30664-2026 artfynd.xlsx
+++ b/artfynd/A 30664-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136420642</v>
       </c>
       <c r="B2" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136420658</v>
       </c>
       <c r="B3" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136420666</v>
       </c>
       <c r="B4" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136420782</v>
       </c>
       <c r="B5" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136420948</v>
       </c>
       <c r="B6" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>136420975</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
